--- a/deliverables/execution-gap-response-template.xlsx
+++ b/deliverables/execution-gap-response-template.xlsx
@@ -698,7 +698,7 @@
         <v>result.frameworkTotal</v>
       </c>
       <c r="D7" t="str">
-        <v>NOT POPULATED — see Known gaps</v>
+        <v>OK (fixed in 3.26)</v>
       </c>
     </row>
     <row r="8">
@@ -712,7 +712,7 @@
         <v>result.executionTotal</v>
       </c>
       <c r="D8" t="str">
-        <v>NOT POPULATED — see Known gaps</v>
+        <v>OK (fixed in 3.26)</v>
       </c>
     </row>
     <row r="9">
@@ -726,7 +726,7 @@
         <v>result.evidenceTotal</v>
       </c>
       <c r="D9" t="str">
-        <v>NOT POPULATED — see Known gaps</v>
+        <v>OK (fixed in 3.26)</v>
       </c>
     </row>
     <row r="10">
@@ -1031,10 +1031,10 @@
         <v>function</v>
       </c>
       <c r="C31" t="str">
-        <v>result.widestGaps joined</v>
+        <v>result.widestGaps joined — two widest, matches the report</v>
       </c>
       <c r="D31" t="str">
-        <v>NOT POPULATED — see Known gaps</v>
+        <v>OK (fixed in 3.26)</v>
       </c>
     </row>
     <row r="32">
@@ -1059,10 +1059,10 @@
         <v>client</v>
       </c>
       <c r="C33" t="str">
-        <v>Venture stage — map only</v>
+        <v>Venture stage</v>
       </c>
       <c r="D33" t="str">
-        <v>map only; blank on unlock</v>
+        <v>OK (fixed in 3.26)</v>
       </c>
     </row>
     <row r="34">
@@ -1073,10 +1073,10 @@
         <v>client</v>
       </c>
       <c r="C34" t="str">
-        <v>'pre' or 'trading' — map only</v>
+        <v>'pre' or 'trading'</v>
       </c>
       <c r="D34" t="str">
-        <v>map only; blank on unlock</v>
+        <v>OK (fixed in 3.26)</v>
       </c>
     </row>
     <row r="35">
@@ -1118,7 +1118,7 @@
         <v>routeFor_() — Focused Session / Mid-Tier / Full Journey</v>
       </c>
       <c r="D37" t="str">
-        <v>OK</v>
+        <v>OK (fixed in 3.26)</v>
       </c>
     </row>
     <row r="38">
@@ -1256,12 +1256,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
     <col min="3" max="3" width="80.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1275,7 +1276,10 @@
         <v>Problem</v>
       </c>
       <c r="D1" t="str">
-        <v>Fix</v>
+        <v>Resolution</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
@@ -1286,10 +1290,13 @@
         <v>frameworkTotal, executionTotal, evidenceTotal</v>
       </c>
       <c r="C2" t="str">
-        <v>The Apps Script reads result.frameworkTotal / .executionTotal / .evidenceTotal, but netlify/functions/execution-gap.ts sends these totals as result.F / result.E / result.V. The names never match, so all three columns record 0 on every submission.</v>
+        <v>The Apps Script reads result.frameworkTotal / .executionTotal / .evidenceTotal, but the function sent these totals as result.F / result.E / result.V. The names never matched, so all three columns recorded 0 on every submission.</v>
       </c>
       <c r="D2" t="str">
-        <v>Either rename the keys in compute() to frameworkTotal/executionTotal/evidenceTotal, or read result.F/.E/.V in map_().</v>
+        <v>compute() now emits both namings. Covered by tests/unit/executionGapFunction.test.ts.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>FIXED 3.26</v>
       </c>
     </row>
     <row r="3">
@@ -1300,10 +1307,13 @@
         <v>widestGaps</v>
       </c>
       <c r="C3" t="str">
-        <v>The Apps Script reads result.widestGaps. The Netlify function never computes or sends that field, so the column is always blank.</v>
+        <v>The Apps Script reads result.widestGaps. The function never computed or sent that field, so the column was always blank.</v>
       </c>
       <c r="D3" t="str">
-        <v>Compute the two widest gaps in the function (the client already derives them for display) and include them in result.</v>
+        <v>compute() now ranks the two widest gaps using the same formula as scoreExecutionGap(), so the sheet records the pair the respondent was actually shown.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>FIXED 3.26</v>
       </c>
     </row>
     <row r="4">
@@ -1311,13 +1321,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>userAgent, referrer</v>
+        <v>route (on unlock)</v>
       </c>
       <c r="C4" t="str">
-        <v>The Apps Script reads body.userAgent and body.referrer. Neither the client nor the function ever sends them, so both columns are always blank.</v>
+        <v>HEADERS is 45 columns, but unlock_() wrote 10 values starting at column 37 (37-46). The 10th value, route, landed in column 46 - one past the last header - instead of the route column at 36.</v>
       </c>
       <c r="D4" t="str">
-        <v>Populate them in the client POST, or drop the two columns.</v>
+        <v>unlock_() now writes 9 values (37-45) and sets column 36 separately.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>FIXED 3.26</v>
       </c>
     </row>
     <row r="5">
@@ -1325,13 +1338,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>route (on unlock)</v>
+        <v>stage, stageBand (on unlock)</v>
       </c>
       <c r="C5" t="str">
-        <v>HEADERS is 45 columns, but unlock_() writes 10 values starting at column 37 (37-46). The 10th value, route, lands in column 46 — one past the last header — instead of the route column at 36.</v>
+        <v>The client's unlock POST omitted stage and stageBand, which the map POST does send. On an unlock that created a fresh row both columns were blank, and routeFor_() misread the band.</v>
       </c>
       <c r="D5" t="str">
-        <v>Write 9 values (37-45) and set column 36 separately, or extend HEADERS.</v>
+        <v>ExecutionGap.tsx now passes stage and stageBand into the unlock body.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>FIXED 3.26</v>
       </c>
     </row>
     <row r="6">
@@ -1339,13 +1355,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>stage, stageBand (on unlock)</v>
+        <v>archetype in the respondent email</v>
       </c>
       <c r="C6" t="str">
-        <v>The client's unlock POST (ExecutionGap.tsx) omits stage and stageBand, which the map POST does send. On an unlock that creates a fresh row, both columns are blank, and routeFor_() misreads the band.</v>
+        <v>sendRespondentEmail_() and sendNotification_() read body.archetype, but the function nests it at result.archetype. Every report email fell back to the generic "Your Loop Map" heading.</v>
       </c>
       <c r="D6" t="str">
-        <v>Include stage and stageBand in the unlock POST body.</v>
+        <v>Both mail helpers now read body.result?.archetype.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>FIXED 3.26</v>
       </c>
     </row>
     <row r="7">
@@ -1353,13 +1372,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>archetype in the respondent email</v>
+        <v>Silent failure (whole sheet)</v>
       </c>
       <c r="C7" t="str">
-        <v>sendRespondentEmail_() and sendNotification_() read body.archetype, but the function nests it at result.archetype. Every report email falls back to the generic "Your Loop Map" heading.</v>
+        <v>Apps Script returns HTTP 200 even when doPost() catches an error, putting the real status in the JSON body as {ok:false}. The function only checked upstream.ok, so a failed sheet write was reported to the browser as success. This is why the live endpoint answered 200 while nothing was captured.</v>
       </c>
       <c r="D7" t="str">
-        <v>Read body.result.archetype in both mail helpers.</v>
+        <v>forward() now parses the response body and throws unless ok is true. NOTE: this makes a broken sheet visible - the unlock form will show an error instead of falsely confirming. That is the intended behaviour.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>FIXED 3.26</v>
       </c>
     </row>
     <row r="8">
@@ -1367,18 +1389,21 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Silent failure (whole sheet)</v>
+        <v>userAgent, referrer</v>
       </c>
       <c r="C8" t="str">
-        <v>Apps Script returns HTTP 200 even when doPost() catches an error, putting the real status in the JSON body as {ok:false}. The Netlify function only checks upstream.ok (the HTTP status), so a failed sheet write still returns success to the browser. This is why the live endpoint returns 200 while nothing is captured.</v>
+        <v>The Apps Script reads body.userAgent and body.referrer. Neither the client nor the function sends them, so both columns are always blank.</v>
       </c>
       <c r="D8" t="str">
-        <v>Parse the Apps Script JSON response in forward() and throw when body.ok is false.</v>
+        <v>Not fixed. Populate them in the client POST, or drop the two columns.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>OUTSTANDING</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/deliverables/execution-gap-response-template.xlsx
+++ b/deliverables/execution-gap-response-template.xlsx
@@ -1199,10 +1199,10 @@
         <v>function</v>
       </c>
       <c r="C43" t="str">
-        <v>Report body sent to the respondent</v>
+        <v>Full report body: archetype, Gap Ledger, two widest gaps, 30-day plan, AI multiplier</v>
       </c>
       <c r="D43" t="str">
-        <v>unlock only</v>
+        <v>unlock only (fixed 3.28)</v>
       </c>
     </row>
     <row r="44">
@@ -1256,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -1389,21 +1389,38 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
+        <v>reportText (duplicate emails)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>forward() ran unconditionally and again for the unlock, so the Apps Script executed unlock_() twice per submission: two report emails to the respondent (the first with an empty body, falling back to a generic line) and two lead notifications to NOTIFY_TO. reportText itself was a hardcoded placeholder sentence, so no actual report was ever sent.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>The handler now forwards exactly once, and buildReport() composes the real report from the same data the respondent saw on screen.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>FIXED 3.28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
         <v>userAgent, referrer</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C9" t="str">
         <v>The Apps Script reads body.userAgent and body.referrer. Neither the client nor the function sends them, so both columns are always blank.</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D9" t="str">
         <v>Not fixed. Populate them in the client POST, or drop the two columns.</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E9" t="str">
         <v>OUTSTANDING</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
